--- a/光伏配储项目/电价数据/2026/双水B厂.xlsx
+++ b/光伏配储项目/电价数据/2026/双水B厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5367799999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.23661</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64388</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.00376</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.8177300000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.7155499999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44107</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42336</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45397</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42603</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42693</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44741</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47346</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.75475</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.60724</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.50857</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.56208</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.5880700000000001</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25876</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.8047300000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.80498</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.80804</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.48983</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.16024</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.53574</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.5297200000000001</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.7989700000000001</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.9116599999999999</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5896699999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.63785</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.62625</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.8273200000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.74246</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.80426</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.0427</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.32298</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.46794</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.71531</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.16094</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.97609</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.83558</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.9920399999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.18054</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9448200000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.71354</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.75968</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.42918</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.15285</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.75949</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.10818</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.20381</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06476</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.44318</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.19497</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.16994</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.12606</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48002</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40621</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41303</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42226</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.07635</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.96674</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.04174</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53743</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5349400000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47315</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7583099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.73122</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45979</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44134</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.83494</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.97868</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.61334</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.8037000000000001</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.83963</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.73429</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.63235</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.50492</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.60845</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.02227</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.05046</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.33262</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.99566</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.26701</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.87483</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.7965</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.1888</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.01758</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.90774</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.48397</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.4962</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.5774900000000001</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47104</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.49706</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.11009</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.95441</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.91134</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.94189</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.85862</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7870900000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.79043</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.55138</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.88021</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.10841</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04267</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.8825700000000001</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.2625</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.49902</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.42999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.50185</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.60734</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.59252</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.75859</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.10317</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.20822</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.93826</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.65947</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.62854</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.79037</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5382400000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.62295</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.64362</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.8040499999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.67422</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6186699999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.62025</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.5015299999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.71556</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.92265</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.26938</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6491699999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.99948</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.31621</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8269</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.8774500000000001</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.68345</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81747</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.96697</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.95012</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.69292</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40706</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.9322699999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.86553</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.97126</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.53919</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.15025</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.1376</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.9749500000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.91338</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.8639199999999999</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.31369</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.2655</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.13337</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.10198</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.09217</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.04203</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.54339</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.91864</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.56788</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.9156599999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.93677</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.92276</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.01773</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.94608</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.0496</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.87598</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.67153</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.6547799999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9200199999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.60673</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.51567</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.5385599999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6001299999999999</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.59215</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33338</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.57704</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.55025</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6692899999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.90713</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.82385</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.6710499999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.05153</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.09365</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.6341100000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.7270700000000001</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.98375</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.96129</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.20088</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.8431000000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.9030199999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.5461</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.68736</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.53232</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.81499</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.96674</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.80848</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.8344600000000001</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.86573</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.80283</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7647699999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.72873</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.9523200000000001</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.00554</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.60909</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.96326</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.90822</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.64493</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.82753</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.87426</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.89925</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.99556</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.96196</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.98921</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.61493</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.91003</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.8716699999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.82497</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.89715</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.93192</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.92765</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.8986499999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.84174</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.44608</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.6132300000000001</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31148</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.56772</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39404</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.24654</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.20397</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28387</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.16603</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.22123</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.23806</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.16989</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.16572</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.16603</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.24749</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18414</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.21211</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.19848</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.19887</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.1601</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.17717</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.18909</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.16632</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.37644</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.51266</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.51148</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.44376</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46466</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40408</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.45228</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31118</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.00906</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.77207</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.80027</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34577</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33949</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22372</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.16216</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20021</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05368</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.02246</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.15977</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.16097</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.16192</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.17857</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.18478</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.18214</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.18451</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33745</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33546</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38851</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.24324</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28714</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.61937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.72799</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.57733</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.57669</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6039800000000001</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.64461</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.80567</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.47356</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.65003</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.63379</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.7559600000000001</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.51423</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14198</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.6061299999999999</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.6047400000000001</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.54541</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.53767</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6650700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7965399999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7365499999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.5428200000000001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.67169</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.95136</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.2666</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.74297</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.28857</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.26413</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.67948</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.67789</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.25086</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.92441</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.63619</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.24846</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.72336</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.65247</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.3341</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.71636</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8078200000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8827</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50895</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46783</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54313</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5032799999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59534</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5838099999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66522</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.81457</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.28516</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.82992</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.14639</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.12371</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.10204</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.48373</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.64349</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.47928</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.53215</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.80531</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.51017</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.48601</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.80521</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.67803</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.37951</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.52864</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.5414500000000001</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.50986</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.5568200000000001</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.53488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5059399999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.53359</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.52839</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.46644</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.6355599999999999</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.53488</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.62505</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.5362</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5488200000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.5332</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.52077</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.51679</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95094</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47629</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47865</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.53792</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39498</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.4064</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.57737</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.48657</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.52427</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.6053200000000001</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.7130299999999999</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.8801599999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.80608</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.68488</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.7618400000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.69712</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.6671699999999999</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.80801</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.44726</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.71456</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.13014</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.72414</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.58408</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.94401</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.6546000000000001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.66953</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.53325</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.18228</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.6190399999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.42988</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.47161</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41417</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41552</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.75273</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44782</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.07699</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.74139</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.36603</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7026699999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79411</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64891</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5828</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.63395</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.62948</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.88737</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.71813</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.5455</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.09467</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.5725399999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.09113</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.13043</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.90825</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.14332</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.6987300000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.86517</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.94497</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.79914</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.81252</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.7857799999999999</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.61472</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.19294</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.48151</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.66064</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.05103</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.59504</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.80563</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.8065099999999999</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.6811</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.73791</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.7151900000000001</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.86156</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.8829400000000001</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.71446</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.89103</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.16043</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.80359</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.80508</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.90073</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.76807</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.10893</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.76647</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.8118500000000001</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.73814</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.71733</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.21413</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.90579</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.49877</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.25363</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.8124600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.8211499999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6500900000000001</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43232</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26157</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27056</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26403</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.54811</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.54586</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30687</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5345800000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.48429</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.59888</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.81076</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.76239</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.60287</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.53992</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.66947</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.79508</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.77651</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.75652</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.46088</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.41143</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.42736</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37357</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.71324</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.71362</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.70292</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.00712</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.01342</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.6393099999999999</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.7736000000000001</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.19299</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.69309</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.18034</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.04513</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.03513</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.12384</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.42344</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.29334</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.44739</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.81413</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.77923</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.6969099999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.03513</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.02013</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.05261</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.06494</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.06007</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.037</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.06013</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.80877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.09527</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.30922</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.17528</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.19982</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.09139</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.09966</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.10706</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.04424</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.14135</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.6918200000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.75291</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.08604</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.09368</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.08814</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.63904</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.17243</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.47468</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.11717</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.25766</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61497</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.66218</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.13357</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.72765</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.41393</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32343</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43054</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.75587</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.55829</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.5671499999999999</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.65918</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.95631</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.80986</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.64511</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.56555</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34926</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.56662</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.11215</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42653</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38602</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56347</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.53918</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6410800000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8162200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.57413</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.55237</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.58456</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.18525</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.42127</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.5336000000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.72961</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.72274</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.00213</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.49817</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.80865</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.66765</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.80521</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.61142</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7872400000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.15152</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.7044900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.91037</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.55633</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.0188</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6238899999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.9453400000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.13356</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.89958</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.65895</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.16136</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.96209</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.77942</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.11795</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.65214</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.72516</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.79918</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.53647</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.4752</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.66494</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.46496</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.52547</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.55036</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74007</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.78642</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.85426</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.33683</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.70445</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.45076</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.38301</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.30721</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.17594</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.87013</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.74786</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.1223</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.44776</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.44651</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5201399999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.6432100000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.91643</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.60521</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.7784800000000001</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.5893200000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.79661</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.78165</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.28069</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.24045</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.92816</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.9316599999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.0819</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.06777</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.43893</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.72756</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.54032</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.11855</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.19282</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.74552</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.77907</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.95139</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.15337</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.83401</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47597</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.01975</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.61424</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48225</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43104</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.61075</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.58428</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.5753200000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.97016</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.87042</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.2469</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.0991</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.65122</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.69425</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7058099999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.46376</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.41713</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36453</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42814</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.4681</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.46665</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42976</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38347</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41715</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.48424</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48273</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.54371</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3915</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.64064</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.84382</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5268999999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43128</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.3285</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.19715</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.2963</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.19395</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.25741</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.19583</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.37335</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.52889</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.49871</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.59333</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.20304</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.24795</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.24114</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.19953</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.18356</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.17886</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.19757</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.17738</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.21936</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.53537</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.25329</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.23599</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.21234</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.17985</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.17244</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.20102</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.17985</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.18507</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.17832</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.29144</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.22314</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37951</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.6424</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30566</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32539</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30552</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.84194</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.8723500000000001</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.49235</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5548500000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5278400000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.41703</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.34876</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.62115</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38461</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.56292</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9195399999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9236</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.04448</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8904099999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.71212</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.9633700000000001</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.42478</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10177</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.47514</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21304</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.15538</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.48671</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.18653</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5248400000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.81847</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.47003</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.62259</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.5447000000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.95169</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.74293</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.7415499999999999</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.7497200000000001</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.75836</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8982899999999999</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.5571</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.7901699999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.59311</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.8164600000000001</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.24358</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.24832</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.27787</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.70257</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.24358</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.34484</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.42466</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.94531</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7932899999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8446</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.16348</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.00524</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.78207</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.5972999999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33773</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.48192</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.64227</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.47021</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5996699999999999</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.60109</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47427</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41759</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.23092</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.7000299999999999</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6370399999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48812</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.50584</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.79762</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.91486</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.8257000000000001</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.92748</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.27495</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.26389</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.83439</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.8578300000000001</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.59981</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.46032</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5111100000000001</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46557</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.45473</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.53224</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.08497</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.70233</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.45899</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.42833</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.4379</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.48226</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.47821</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.48344</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.45862</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45843</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.5534199999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.9036799999999999</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.85375</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.55213</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.00678</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.69537</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.58399</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.90042</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.73354</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46602</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46674</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.4660899999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33955</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43513</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41763</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58962</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5633400000000001</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.84537</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.12986</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.55153</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6780700000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.7915</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.83085</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.77947</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.7522000000000001</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.78589</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.76462</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.7644299999999999</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.17766</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.74834</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.51993</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.7593</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.76661</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.6002</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.74805</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.6284</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.76093</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7332000000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.04992</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.24692</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.27108</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.29393</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.35401</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.34501</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.40246</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.4491</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.42654</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9965599999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.87767</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.83788</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48251</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.04859</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.81229</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.87786</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.76542</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.69496</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.68149</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.68653</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.65287</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6957300000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.55359</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.58313</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.65403</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.61614</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.68747</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44019</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69589</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.5510499999999999</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7083400000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6073200000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6077100000000001</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.5230199999999999</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.64218</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.64511</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.83504</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.69325</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.83392</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.76562</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.85192</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.83092</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.82892</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.04223</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06065</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.80192</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.50554</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.5881000000000001</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.6127100000000001</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.6893400000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.67175</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.72612</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.22502</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.22819</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.52611</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.25381</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.52449</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.50649</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.53739</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.27769</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.91543</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.89639</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.56735</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.64242</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.30971</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.31044</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.12574</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.53853</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.63548</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.61793</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.07155</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.0309</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.76532</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.27531</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.23406</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.54261</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.30661</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.30725</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.67028</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.6527500000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.6397699999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37561</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.59793</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.58549</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.88205</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.70587</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.63085</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.65786</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.82713</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.8460599999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.96496</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5762999999999999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.2579</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.02005</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.97733</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.67653</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.47833</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17162</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.5905199999999999</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.33513</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.18307</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.6589700000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.22821</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.6616599999999999</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.74121</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.6545299999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.75748</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.52966</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.8442799999999999</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.67048</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.76703</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.62246</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.75183</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.84023</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8998200000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.75659</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.77044</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.74521</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.75078</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.76263</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.10101</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.14886</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.05175</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.06567</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.24854</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.00654</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.04031</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.82147</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.80275</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.81804</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.85833</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.85897</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.84276</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.9518099999999999</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.62129</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.5916399999999999</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.51488</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37601</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.31842</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.91374</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9421900000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.22215</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45425</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.6348200000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.50605</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.60057</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.60142</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.56621</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.71316</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.60341</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.72629</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.29121</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.8020700000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.8684299999999999</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9747899999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.96351</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.8645499999999999</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.06943</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.8228099999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.46839</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.17834</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.44208</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.54243</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.68521</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.8380599999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.62462</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.41037</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.5438999999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.0073</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.84127</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.59929</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.26817</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.8452999999999999</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.38856</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.23543</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.05006</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.9000900000000001</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.86426</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.8679199999999999</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.86277</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.87252</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.87958</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.91908</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.39946</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.50295</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.8471799999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.8630099999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.8446699999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.90091</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.66633</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.07723</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.62898</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.60602</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.48506</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.97564</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.6442100000000001</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.6454</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.44981</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.47164</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.47425</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.46071</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.44212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.40074</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.7403200000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.5758099999999999</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.87119</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.15512</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.8164600000000001</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.8717999999999999</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5445599999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.51781</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.49631</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.28309</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.88988</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.68772</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.41145</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.57285</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.52381</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.6963200000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.5389700000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.86073</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.74519</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7554999999999999</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.78015</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.79965</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.58661</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5591799999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.54071</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.55253</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.63934</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.63849</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.52435</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.6385599999999999</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6395700000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.92336</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.6725099999999999</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.56652</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.57337</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.55821</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5166900000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.65115</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.61738</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.6842</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.5607000000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5205299999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37242</v>
       </c>
     </row>
   </sheetData>
